--- a/survey_templates/043_hiv_policy_feedback_survey--survey_templates.xlsx
+++ b/survey_templates/043_hiv_policy_feedback_survey--survey_templates.xlsx
@@ -1,15 +1,15 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="survey" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="choices" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet name="settings" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="survey" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="choices" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="settings" sheetId="3" state="visible" r:id="rId3"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -437,12 +437,12 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E30"/>
+  <dimension ref="A1:E21"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="17" customWidth="1" min="1" max="1"/>
-    <col width="32" customWidth="1" min="2" max="2"/>
-    <col width="32" customWidth="1" min="3" max="3"/>
+    <col width="25" customWidth="1" min="2" max="2"/>
+    <col width="50" customWidth="1" min="3" max="3"/>
     <col width="41" customWidth="1" min="4" max="4"/>
     <col width="10" customWidth="1" min="5" max="5"/>
   </cols>
@@ -525,13 +525,13 @@
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>region</t>
+          <t>Which region has the greatest need for HIV policy support?</t>
         </is>
       </c>
       <c r="D4" t="inlineStr"/>
       <c r="E4" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>yes</t>
         </is>
       </c>
     </row>
@@ -543,18 +543,18 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>feedback_effectiveness</t>
+          <t>policy_effectiveness</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>policy_effectiveness</t>
+          <t>How would you rate the effectiveness of the HIV policy?</t>
         </is>
       </c>
       <c r="D5" t="inlineStr"/>
       <c r="E5" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>yes</t>
         </is>
       </c>
     </row>
@@ -571,13 +571,13 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>implementation_barriers</t>
+          <t>What are the barriers to implementing the HIV policy?</t>
         </is>
       </c>
       <c r="D6" t="inlineStr"/>
       <c r="E6" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>yes</t>
         </is>
       </c>
     </row>
@@ -594,63 +594,59 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>improvement_priorities</t>
+          <t>What are the priorities for improving the HIV policy?</t>
         </is>
       </c>
       <c r="D7" t="inlineStr"/>
       <c r="E7" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>yes</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>select_multiple</t>
+          <t>text</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>policy_implementation_barriers</t>
+          <t>contact_name</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>policy_implementation_barriers</t>
+          <t>What is your name?</t>
         </is>
       </c>
       <c r="D8" t="inlineStr"/>
       <c r="E8" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>yes</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>note</t>
+          <t>text</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>note</t>
+          <t>contact_email</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>additional_feedback</t>
-        </is>
-      </c>
-      <c r="D9" t="inlineStr">
-        <is>
-          <t>Please provide any additional feedback.</t>
-        </is>
-      </c>
+          <t>What is your email address?</t>
+        </is>
+      </c>
+      <c r="D9" t="inlineStr"/>
       <c r="E9" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>yes</t>
         </is>
       </c>
     </row>
@@ -662,18 +658,18 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>contact_name</t>
+          <t>contact_phone</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>contact_name</t>
+          <t>What is your phone number?</t>
         </is>
       </c>
       <c r="D10" t="inlineStr"/>
       <c r="E10" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>yes</t>
         </is>
       </c>
     </row>
@@ -685,180 +681,184 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>contact_email</t>
+          <t>contact_address</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>contact_email</t>
+          <t>What is your address?</t>
         </is>
       </c>
       <c r="D11" t="inlineStr"/>
       <c r="E11" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>yes</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>text</t>
+          <t>select_one</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>contact_phone</t>
+          <t>form_submitted</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>contact_phone</t>
+          <t>Have you already submitted this form?</t>
         </is>
       </c>
       <c r="D12" t="inlineStr"/>
       <c r="E12" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>yes</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>text</t>
+          <t>date</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>contact_phone_extension</t>
+          <t>date_submitted</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>contact_phone_extension</t>
+          <t>On what date did you submit this form?</t>
         </is>
       </c>
       <c r="D13" t="inlineStr"/>
       <c r="E13" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>yes</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>text</t>
+          <t>time</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>contact_address</t>
+          <t>time_submitted</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>contact_address</t>
+          <t>On what time did you submit this form?</t>
         </is>
       </c>
       <c r="D14" t="inlineStr"/>
       <c r="E14" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>yes</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>text</t>
+          <t>select_one</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>contact_zip</t>
+          <t>region_2</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>contact_zip</t>
+          <t>Is your region in need of policy support?</t>
         </is>
       </c>
       <c r="D15" t="inlineStr"/>
       <c r="E15" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>yes</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>select_one</t>
+          <t>note</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>form_submitted</t>
+          <t>note</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>submit</t>
-        </is>
-      </c>
-      <c r="D16" t="inlineStr"/>
+          <t>Do you have any additional feedback?</t>
+        </is>
+      </c>
+      <c r="D16" t="inlineStr">
+        <is>
+          <t>Please provide any additional feedback.</t>
+        </is>
+      </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>yes</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>note</t>
+          <t>select_one</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>additional_feedback</t>
+          <t>region_3</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>additional_feedback</t>
-        </is>
-      </c>
-      <c r="D17" t="inlineStr">
-        <is>
-          <t>Please provide any additional feedback.</t>
-        </is>
-      </c>
+          <t>Region 3</t>
+        </is>
+      </c>
+      <c r="D17" t="inlineStr"/>
       <c r="E17" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>yes</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>date</t>
+          <t>note</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>date_submitted</t>
+          <t>additional_feedback</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>date_submitted</t>
-        </is>
-      </c>
-      <c r="D18" t="inlineStr"/>
+          <t>Additional feedback</t>
+        </is>
+      </c>
+      <c r="D18" t="inlineStr">
+        <is>
+          <t>Please provide any additional feedback.</t>
+        </is>
+      </c>
       <c r="E18" t="inlineStr">
         <is>
           <t>no</t>
@@ -868,17 +868,17 @@
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>time</t>
+          <t>select_one</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>time_submitted</t>
+          <t>region_4</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>time_submitted</t>
+          <t>Region</t>
         </is>
       </c>
       <c r="D19" t="inlineStr"/>
@@ -896,12 +896,12 @@
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>region</t>
+          <t>region_5</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>region</t>
+          <t>Region 5</t>
         </is>
       </c>
       <c r="D20" t="inlineStr"/>
@@ -919,227 +919,16 @@
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>region</t>
+          <t>region_6</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>region</t>
+          <t>Region 6</t>
         </is>
       </c>
       <c r="D21" t="inlineStr"/>
       <c r="E21" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
-    </row>
-    <row r="22">
-      <c r="A22" t="inlineStr">
-        <is>
-          <t>select_multiple</t>
-        </is>
-      </c>
-      <c r="B22" t="inlineStr">
-        <is>
-          <t>feedback_effectiveness</t>
-        </is>
-      </c>
-      <c r="C22" t="inlineStr">
-        <is>
-          <t>policy_effectiveness</t>
-        </is>
-      </c>
-      <c r="D22" t="inlineStr"/>
-      <c r="E22" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
-    </row>
-    <row r="23">
-      <c r="A23" t="inlineStr">
-        <is>
-          <t>select_multiple</t>
-        </is>
-      </c>
-      <c r="B23" t="inlineStr">
-        <is>
-          <t>barriers_implementation</t>
-        </is>
-      </c>
-      <c r="C23" t="inlineStr">
-        <is>
-          <t>implementation_barriers</t>
-        </is>
-      </c>
-      <c r="D23" t="inlineStr"/>
-      <c r="E23" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
-    </row>
-    <row r="24">
-      <c r="A24" t="inlineStr">
-        <is>
-          <t>select_multiple</t>
-        </is>
-      </c>
-      <c r="B24" t="inlineStr">
-        <is>
-          <t>improvement_priorities</t>
-        </is>
-      </c>
-      <c r="C24" t="inlineStr">
-        <is>
-          <t>improvement_priorities</t>
-        </is>
-      </c>
-      <c r="D24" t="inlineStr"/>
-      <c r="E24" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
-    </row>
-    <row r="25">
-      <c r="A25" t="inlineStr">
-        <is>
-          <t>select_multiple</t>
-        </is>
-      </c>
-      <c r="B25" t="inlineStr">
-        <is>
-          <t>policy_implementation_barriers</t>
-        </is>
-      </c>
-      <c r="C25" t="inlineStr">
-        <is>
-          <t>policy_implementation_barriers</t>
-        </is>
-      </c>
-      <c r="D25" t="inlineStr"/>
-      <c r="E25" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
-    </row>
-    <row r="26">
-      <c r="A26" t="inlineStr">
-        <is>
-          <t>select_multiple</t>
-        </is>
-      </c>
-      <c r="B26" t="inlineStr">
-        <is>
-          <t>policy_implementation_barriers</t>
-        </is>
-      </c>
-      <c r="C26" t="inlineStr">
-        <is>
-          <t>policy_implementation_barriers</t>
-        </is>
-      </c>
-      <c r="D26" t="inlineStr"/>
-      <c r="E26" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
-    </row>
-    <row r="27">
-      <c r="A27" t="inlineStr">
-        <is>
-          <t>note</t>
-        </is>
-      </c>
-      <c r="B27" t="inlineStr">
-        <is>
-          <t>note</t>
-        </is>
-      </c>
-      <c r="C27" t="inlineStr">
-        <is>
-          <t>additional_feedback</t>
-        </is>
-      </c>
-      <c r="D27" t="inlineStr">
-        <is>
-          <t>Please provide any additional feedback.</t>
-        </is>
-      </c>
-      <c r="E27" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
-    </row>
-    <row r="28">
-      <c r="A28" t="inlineStr">
-        <is>
-          <t>text</t>
-        </is>
-      </c>
-      <c r="B28" t="inlineStr">
-        <is>
-          <t>contact_phone</t>
-        </is>
-      </c>
-      <c r="C28" t="inlineStr">
-        <is>
-          <t>contact_phone</t>
-        </is>
-      </c>
-      <c r="D28" t="inlineStr"/>
-      <c r="E28" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
-    </row>
-    <row r="29">
-      <c r="A29" t="inlineStr">
-        <is>
-          <t>select_one</t>
-        </is>
-      </c>
-      <c r="B29" t="inlineStr">
-        <is>
-          <t>region</t>
-        </is>
-      </c>
-      <c r="C29" t="inlineStr">
-        <is>
-          <t>region</t>
-        </is>
-      </c>
-      <c r="D29" t="inlineStr"/>
-      <c r="E29" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
-    </row>
-    <row r="30">
-      <c r="A30" t="inlineStr">
-        <is>
-          <t>select_one</t>
-        </is>
-      </c>
-      <c r="B30" t="inlineStr">
-        <is>
-          <t>region</t>
-        </is>
-      </c>
-      <c r="C30" t="inlineStr">
-        <is>
-          <t>region</t>
-        </is>
-      </c>
-      <c r="D30" t="inlineStr"/>
-      <c r="E30" t="inlineStr">
         <is>
           <t>no</t>
         </is>
@@ -1156,10 +945,10 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C62"/>
+  <dimension ref="A1:C35"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="40" customWidth="1" min="1" max="1"/>
+    <col width="33" customWidth="1" min="1" max="1"/>
     <col width="30" customWidth="1" min="2" max="2"/>
     <col width="30" customWidth="1" min="3" max="3"/>
   </cols>
@@ -1252,7 +1041,7 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>feedback_effectiveness_choices</t>
+          <t>policy_effectiveness_choices</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -1269,7 +1058,7 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>feedback_effectiveness_choices</t>
+          <t>policy_effectiveness_choices</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
@@ -1286,7 +1075,7 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>feedback_effectiveness_choices</t>
+          <t>policy_effectiveness_choices</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
@@ -1303,7 +1092,7 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>feedback_effectiveness_choices</t>
+          <t>policy_effectiveness_choices</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
@@ -1490,729 +1279,270 @@
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>policy_implementation_barriers_choices</t>
+          <t>form_submitted_choices</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>lack_of_funding</t>
+          <t>true</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>Lack of Funding</t>
+          <t>True</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>policy_implementation_barriers_choices</t>
+          <t>form_submitted_choices</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>lack_of_community_engagement</t>
+          <t>false</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>Lack of Community Engagement</t>
+          <t>False</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>policy_implementation_barriers_choices</t>
+          <t>region_2_choices</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>lack_of_awareness</t>
+          <t>true</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>Lack of Awareness</t>
+          <t>True</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>policy_implementation_barriers_choices</t>
+          <t>region_2_choices</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>lack_of_policy_enforcement</t>
+          <t>false</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>Lack of Policy Enforcement</t>
+          <t>False</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>policy_implementation_barriers_choices</t>
+          <t>region_3_choices</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>other_(please_specify)</t>
+          <t>africa</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>Other (please specify)</t>
+          <t>Africa</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>form_submitted_choices</t>
+          <t>region_3_choices</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>true</t>
+          <t>americas</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>True</t>
+          <t>Americas</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>form_submitted_choices</t>
+          <t>region_3_choices</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>false</t>
+          <t>asia</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>Asia</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>region_choices</t>
+          <t>region_3_choices</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>africa</t>
+          <t>europe</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>Africa</t>
+          <t>Europe</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>region_choices</t>
+          <t>region_4_choices</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>americas</t>
+          <t>africa</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>Americas</t>
+          <t>Africa</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>region_choices</t>
+          <t>region_4_choices</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>asia</t>
+          <t>americas</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>Asia</t>
+          <t>Americas</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>region_choices</t>
+          <t>region_4_choices</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>europe</t>
+          <t>asia</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>Europe</t>
+          <t>Asia</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>region_choices</t>
+          <t>region_4_choices</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>africa</t>
+          <t>europe</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>Africa</t>
+          <t>Europe</t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>region_choices</t>
+          <t>region_5_choices</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>americas</t>
+          <t>yes</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>Americas</t>
+          <t>Yes</t>
         </is>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>region_choices</t>
+          <t>region_5_choices</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>asia</t>
+          <t>no</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>Asia</t>
+          <t>No</t>
         </is>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>region_choices</t>
+          <t>region_6_choices</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>europe</t>
+          <t>yes</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>Europe</t>
+          <t>Yes</t>
         </is>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>feedback_effectiveness_choices</t>
+          <t>region_6_choices</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>very_effective</t>
+          <t>no</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
-        <is>
-          <t>Very Effective</t>
-        </is>
-      </c>
-    </row>
-    <row r="36">
-      <c r="A36" t="inlineStr">
-        <is>
-          <t>feedback_effectiveness_choices</t>
-        </is>
-      </c>
-      <c r="B36" t="inlineStr">
-        <is>
-          <t>somewhat_effective</t>
-        </is>
-      </c>
-      <c r="C36" t="inlineStr">
-        <is>
-          <t>Somewhat Effective</t>
-        </is>
-      </c>
-    </row>
-    <row r="37">
-      <c r="A37" t="inlineStr">
-        <is>
-          <t>feedback_effectiveness_choices</t>
-        </is>
-      </c>
-      <c r="B37" t="inlineStr">
-        <is>
-          <t>not_very_effective</t>
-        </is>
-      </c>
-      <c r="C37" t="inlineStr">
-        <is>
-          <t>Not Very Effective</t>
-        </is>
-      </c>
-    </row>
-    <row r="38">
-      <c r="A38" t="inlineStr">
-        <is>
-          <t>feedback_effectiveness_choices</t>
-        </is>
-      </c>
-      <c r="B38" t="inlineStr">
-        <is>
-          <t>not_effective_at_all</t>
-        </is>
-      </c>
-      <c r="C38" t="inlineStr">
-        <is>
-          <t>Not Effective At All</t>
-        </is>
-      </c>
-    </row>
-    <row r="39">
-      <c r="A39" t="inlineStr">
-        <is>
-          <t>barriers_implementation_choices</t>
-        </is>
-      </c>
-      <c r="B39" t="inlineStr">
-        <is>
-          <t>lack_of_funding</t>
-        </is>
-      </c>
-      <c r="C39" t="inlineStr">
-        <is>
-          <t>Lack of Funding</t>
-        </is>
-      </c>
-    </row>
-    <row r="40">
-      <c r="A40" t="inlineStr">
-        <is>
-          <t>barriers_implementation_choices</t>
-        </is>
-      </c>
-      <c r="B40" t="inlineStr">
-        <is>
-          <t>lack_of_community_engagement</t>
-        </is>
-      </c>
-      <c r="C40" t="inlineStr">
-        <is>
-          <t>Lack of Community Engagement</t>
-        </is>
-      </c>
-    </row>
-    <row r="41">
-      <c r="A41" t="inlineStr">
-        <is>
-          <t>barriers_implementation_choices</t>
-        </is>
-      </c>
-      <c r="B41" t="inlineStr">
-        <is>
-          <t>lack_of_awareness</t>
-        </is>
-      </c>
-      <c r="C41" t="inlineStr">
-        <is>
-          <t>Lack of Awareness</t>
-        </is>
-      </c>
-    </row>
-    <row r="42">
-      <c r="A42" t="inlineStr">
-        <is>
-          <t>barriers_implementation_choices</t>
-        </is>
-      </c>
-      <c r="B42" t="inlineStr">
-        <is>
-          <t>lack_of_policy_enforcement</t>
-        </is>
-      </c>
-      <c r="C42" t="inlineStr">
-        <is>
-          <t>Lack of Policy Enforcement</t>
-        </is>
-      </c>
-    </row>
-    <row r="43">
-      <c r="A43" t="inlineStr">
-        <is>
-          <t>barriers_implementation_choices</t>
-        </is>
-      </c>
-      <c r="B43" t="inlineStr">
-        <is>
-          <t>other_(please_specify)</t>
-        </is>
-      </c>
-      <c r="C43" t="inlineStr">
-        <is>
-          <t>Other (please specify)</t>
-        </is>
-      </c>
-    </row>
-    <row r="44">
-      <c r="A44" t="inlineStr">
-        <is>
-          <t>improvement_priorities_choices</t>
-        </is>
-      </c>
-      <c r="B44" t="inlineStr">
-        <is>
-          <t>increase_funding</t>
-        </is>
-      </c>
-      <c r="C44" t="inlineStr">
-        <is>
-          <t>Increase Funding</t>
-        </is>
-      </c>
-    </row>
-    <row r="45">
-      <c r="A45" t="inlineStr">
-        <is>
-          <t>improvement_priorities_choices</t>
-        </is>
-      </c>
-      <c r="B45" t="inlineStr">
-        <is>
-          <t>improve_awareness</t>
-        </is>
-      </c>
-      <c r="C45" t="inlineStr">
-        <is>
-          <t>Improve Awareness</t>
-        </is>
-      </c>
-    </row>
-    <row r="46">
-      <c r="A46" t="inlineStr">
-        <is>
-          <t>improvement_priorities_choices</t>
-        </is>
-      </c>
-      <c r="B46" t="inlineStr">
-        <is>
-          <t>enhance_community_engagement</t>
-        </is>
-      </c>
-      <c r="C46" t="inlineStr">
-        <is>
-          <t>Enhance Community Engagement</t>
-        </is>
-      </c>
-    </row>
-    <row r="47">
-      <c r="A47" t="inlineStr">
-        <is>
-          <t>improvement_priorities_choices</t>
-        </is>
-      </c>
-      <c r="B47" t="inlineStr">
-        <is>
-          <t>improve_policy_enforcement</t>
-        </is>
-      </c>
-      <c r="C47" t="inlineStr">
-        <is>
-          <t>Improve Policy Enforcement</t>
-        </is>
-      </c>
-    </row>
-    <row r="48">
-      <c r="A48" t="inlineStr">
-        <is>
-          <t>improvement_priorities_choices</t>
-        </is>
-      </c>
-      <c r="B48" t="inlineStr">
-        <is>
-          <t>other_(please_specify)</t>
-        </is>
-      </c>
-      <c r="C48" t="inlineStr">
-        <is>
-          <t>Other (please specify)</t>
-        </is>
-      </c>
-    </row>
-    <row r="49">
-      <c r="A49" t="inlineStr">
-        <is>
-          <t>policy_implementation_barriers_choices</t>
-        </is>
-      </c>
-      <c r="B49" t="inlineStr">
-        <is>
-          <t>lack_of_funding</t>
-        </is>
-      </c>
-      <c r="C49" t="inlineStr">
-        <is>
-          <t>Lack of Funding</t>
-        </is>
-      </c>
-    </row>
-    <row r="50">
-      <c r="A50" t="inlineStr">
-        <is>
-          <t>policy_implementation_barriers_choices</t>
-        </is>
-      </c>
-      <c r="B50" t="inlineStr">
-        <is>
-          <t>lack_of_community_engagement</t>
-        </is>
-      </c>
-      <c r="C50" t="inlineStr">
-        <is>
-          <t>Lack of Community Engagement</t>
-        </is>
-      </c>
-    </row>
-    <row r="51">
-      <c r="A51" t="inlineStr">
-        <is>
-          <t>policy_implementation_barriers_choices</t>
-        </is>
-      </c>
-      <c r="B51" t="inlineStr">
-        <is>
-          <t>lack_of_awareness</t>
-        </is>
-      </c>
-      <c r="C51" t="inlineStr">
-        <is>
-          <t>Lack of Awareness</t>
-        </is>
-      </c>
-    </row>
-    <row r="52">
-      <c r="A52" t="inlineStr">
-        <is>
-          <t>policy_implementation_barriers_choices</t>
-        </is>
-      </c>
-      <c r="B52" t="inlineStr">
-        <is>
-          <t>lack_of_policy_enforcement</t>
-        </is>
-      </c>
-      <c r="C52" t="inlineStr">
-        <is>
-          <t>Lack of Policy Enforcement</t>
-        </is>
-      </c>
-    </row>
-    <row r="53">
-      <c r="A53" t="inlineStr">
-        <is>
-          <t>policy_implementation_barriers_choices</t>
-        </is>
-      </c>
-      <c r="B53" t="inlineStr">
-        <is>
-          <t>other_(please_specify)</t>
-        </is>
-      </c>
-      <c r="C53" t="inlineStr">
-        <is>
-          <t>Other (please specify)</t>
-        </is>
-      </c>
-    </row>
-    <row r="54">
-      <c r="A54" t="inlineStr">
-        <is>
-          <t>policy_implementation_barriers_choices</t>
-        </is>
-      </c>
-      <c r="B54" t="inlineStr">
-        <is>
-          <t>lack_of_funding</t>
-        </is>
-      </c>
-      <c r="C54" t="inlineStr">
-        <is>
-          <t>Lack of Funding</t>
-        </is>
-      </c>
-    </row>
-    <row r="55">
-      <c r="A55" t="inlineStr">
-        <is>
-          <t>policy_implementation_barriers_choices</t>
-        </is>
-      </c>
-      <c r="B55" t="inlineStr">
-        <is>
-          <t>lack_of_community_engagement</t>
-        </is>
-      </c>
-      <c r="C55" t="inlineStr">
-        <is>
-          <t>Lack of Community Engagement</t>
-        </is>
-      </c>
-    </row>
-    <row r="56">
-      <c r="A56" t="inlineStr">
-        <is>
-          <t>policy_implementation_barriers_choices</t>
-        </is>
-      </c>
-      <c r="B56" t="inlineStr">
-        <is>
-          <t>lack_of_awareness</t>
-        </is>
-      </c>
-      <c r="C56" t="inlineStr">
-        <is>
-          <t>Lack of Awareness</t>
-        </is>
-      </c>
-    </row>
-    <row r="57">
-      <c r="A57" t="inlineStr">
-        <is>
-          <t>policy_implementation_barriers_choices</t>
-        </is>
-      </c>
-      <c r="B57" t="inlineStr">
-        <is>
-          <t>lack_of_policy_enforcement</t>
-        </is>
-      </c>
-      <c r="C57" t="inlineStr">
-        <is>
-          <t>Lack of Policy Enforcement</t>
-        </is>
-      </c>
-    </row>
-    <row r="58">
-      <c r="A58" t="inlineStr">
-        <is>
-          <t>policy_implementation_barriers_choices</t>
-        </is>
-      </c>
-      <c r="B58" t="inlineStr">
-        <is>
-          <t>other_(please_specify)</t>
-        </is>
-      </c>
-      <c r="C58" t="inlineStr">
-        <is>
-          <t>Other (please specify)</t>
-        </is>
-      </c>
-    </row>
-    <row r="59">
-      <c r="A59" t="inlineStr">
-        <is>
-          <t>region_choices</t>
-        </is>
-      </c>
-      <c r="B59" t="inlineStr">
-        <is>
-          <t>yes</t>
-        </is>
-      </c>
-      <c r="C59" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-    </row>
-    <row r="60">
-      <c r="A60" t="inlineStr">
-        <is>
-          <t>region_choices</t>
-        </is>
-      </c>
-      <c r="B60" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
-      <c r="C60" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-    </row>
-    <row r="61">
-      <c r="A61" t="inlineStr">
-        <is>
-          <t>region_choices</t>
-        </is>
-      </c>
-      <c r="B61" t="inlineStr">
-        <is>
-          <t>yes</t>
-        </is>
-      </c>
-      <c r="C61" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-    </row>
-    <row r="62">
-      <c r="A62" t="inlineStr">
-        <is>
-          <t>region_choices</t>
-        </is>
-      </c>
-      <c r="B62" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
-      <c r="C62" t="inlineStr">
         <is>
           <t>No</t>
         </is>
